--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_AS MONACO.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_AS MONACO.xlsx
@@ -565,13 +565,13 @@
         <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>48.8733</v>
+        <v>43.1356</v>
       </c>
       <c r="E2" t="n">
-        <v>34.0449</v>
+        <v>32.165</v>
       </c>
       <c r="F2" t="n">
-        <v>14.8282</v>
+        <v>10.97</v>
       </c>
       <c r="G2" t="n">
         <v>1.5813</v>
@@ -610,13 +610,13 @@
         <v>45.6949</v>
       </c>
       <c r="S2" t="n">
-        <v>9.9621</v>
+        <v>4.2242</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6982</v>
+        <v>-0.1816000000000002</v>
       </c>
       <c r="U2" t="n">
-        <v>8.264099999999999</v>
+        <v>4.4056</v>
       </c>
       <c r="V2" t="n">
         <v>18.5421</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. THEIS</t>
+          <t>M. STRAZEL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>31.2876</v>
+        <v>30.9073</v>
       </c>
       <c r="E3" t="n">
-        <v>41.9354</v>
+        <v>21.103</v>
       </c>
       <c r="F3" t="n">
-        <v>-10.6475</v>
+        <v>9.8041</v>
       </c>
       <c r="G3" t="n">
-        <v>-5.939999999999999</v>
+        <v>26.5309</v>
       </c>
       <c r="H3" t="n">
-        <v>17.8647</v>
+        <v>6.365100000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-23.8048</v>
+        <v>20.1658</v>
       </c>
       <c r="J3" t="n">
-        <v>35.2675</v>
+        <v>65.9825</v>
       </c>
       <c r="K3" t="n">
-        <v>39.8404</v>
+        <v>24.3975</v>
       </c>
       <c r="L3" t="n">
-        <v>-4.572800000000001</v>
+        <v>41.5853</v>
       </c>
       <c r="M3" t="n">
-        <v>-41.2078</v>
+        <v>-39.4516</v>
       </c>
       <c r="N3" t="n">
-        <v>-21.9758</v>
+        <v>-18.0323</v>
       </c>
       <c r="O3" t="n">
-        <v>-19.2322</v>
+        <v>-21.4197</v>
       </c>
       <c r="P3" t="n">
-        <v>9.278499999999999</v>
+        <v>-10.2059</v>
       </c>
       <c r="Q3" t="n">
-        <v>-39.8964</v>
+        <v>-77.4722</v>
       </c>
       <c r="R3" t="n">
-        <v>49.1744</v>
+        <v>67.2663</v>
       </c>
       <c r="S3" t="n">
-        <v>28.9113</v>
+        <v>-11.1821</v>
       </c>
       <c r="T3" t="n">
-        <v>19.0978</v>
+        <v>-8.7014</v>
       </c>
       <c r="U3" t="n">
-        <v>9.8133</v>
+        <v>-2.4806</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9614999999999998</v>
+        <v>25.7639</v>
       </c>
       <c r="W3" t="n">
-        <v>27.4655</v>
+        <v>41.2934</v>
       </c>
       <c r="X3" t="n">
-        <v>-28.427</v>
+        <v>-15.5294</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>26.0777</v>
+        <v>23.0067</v>
       </c>
       <c r="E4" t="n">
-        <v>17.492</v>
+        <v>13.588</v>
       </c>
       <c r="F4" t="n">
-        <v>8.585599999999999</v>
+        <v>9.4191</v>
       </c>
       <c r="G4" t="n">
         <v>5.3656</v>
@@ -766,13 +766,13 @@
         <v>20.4124</v>
       </c>
       <c r="S4" t="n">
-        <v>7.0041</v>
+        <v>3.9332</v>
       </c>
       <c r="T4" t="n">
-        <v>6.061500000000001</v>
+        <v>2.1573</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9427000000000001</v>
+        <v>1.7762</v>
       </c>
       <c r="V4" t="n">
         <v>-2.0648</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>M. JAMES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>24.8584</v>
+        <v>22.4625</v>
       </c>
       <c r="E5" t="n">
-        <v>26.7105</v>
+        <v>23.8931</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.851599999999999</v>
+        <v>-1.4308</v>
       </c>
       <c r="G5" t="n">
-        <v>2.567500000000001</v>
+        <v>-6.4212</v>
       </c>
       <c r="H5" t="n">
-        <v>6.8409</v>
+        <v>-7.079800000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.2736</v>
+        <v>0.6579999999999995</v>
       </c>
       <c r="J5" t="n">
-        <v>21.9865</v>
+        <v>47.6589</v>
       </c>
       <c r="K5" t="n">
-        <v>12.6887</v>
+        <v>17.2074</v>
       </c>
       <c r="L5" t="n">
-        <v>9.297800000000001</v>
+        <v>30.452</v>
       </c>
       <c r="M5" t="n">
-        <v>-19.419</v>
+        <v>-54.0806</v>
       </c>
       <c r="N5" t="n">
-        <v>-5.8476</v>
+        <v>-24.2865</v>
       </c>
       <c r="O5" t="n">
-        <v>-13.5715</v>
+        <v>-29.7937</v>
       </c>
       <c r="P5" t="n">
-        <v>16.9325</v>
+        <v>-17.6285</v>
       </c>
       <c r="Q5" t="n">
-        <v>-34.0974</v>
+        <v>-94.8686</v>
       </c>
       <c r="R5" t="n">
-        <v>51.0298</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>20.9678</v>
+        <v>-8.4048</v>
       </c>
       <c r="T5" t="n">
-        <v>24.7576</v>
+        <v>-7.7799</v>
       </c>
       <c r="U5" t="n">
-        <v>-3.7902</v>
+        <v>-0.6243999999999997</v>
       </c>
       <c r="V5" t="n">
-        <v>-15.609</v>
+        <v>54.9172</v>
       </c>
       <c r="W5" t="n">
-        <v>14.063</v>
+        <v>78.8824</v>
       </c>
       <c r="X5" t="n">
-        <v>-29.672</v>
+        <v>-23.9653</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BLOSSOMGAME</t>
+          <t>N. NEDOVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>14.8172</v>
+        <v>19.4893</v>
       </c>
       <c r="E6" t="n">
-        <v>18.0807</v>
+        <v>10.5637</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.263400000000001</v>
+        <v>8.926000000000002</v>
       </c>
       <c r="G6" t="n">
-        <v>-22.4868</v>
+        <v>12.9999</v>
       </c>
       <c r="H6" t="n">
-        <v>11.2027</v>
+        <v>4.5888</v>
       </c>
       <c r="I6" t="n">
-        <v>-33.689</v>
+        <v>8.410600000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>26.4171</v>
+        <v>26.255</v>
       </c>
       <c r="K6" t="n">
-        <v>33.0154</v>
+        <v>10.2915</v>
       </c>
       <c r="L6" t="n">
-        <v>-6.598400000000001</v>
+        <v>15.9639</v>
       </c>
       <c r="M6" t="n">
-        <v>-48.9038</v>
+        <v>-13.2553</v>
       </c>
       <c r="N6" t="n">
-        <v>-21.8131</v>
+        <v>-5.7022</v>
       </c>
       <c r="O6" t="n">
-        <v>-27.091</v>
+        <v>-7.5529</v>
       </c>
       <c r="P6" t="n">
-        <v>30.8499</v>
+        <v>9.0463</v>
       </c>
       <c r="Q6" t="n">
-        <v>-34.3294</v>
+        <v>-25.2833</v>
       </c>
       <c r="R6" t="n">
-        <v>65.1789</v>
+        <v>34.3292</v>
       </c>
       <c r="S6" t="n">
-        <v>9.263300000000001</v>
+        <v>-2.9996</v>
       </c>
       <c r="T6" t="n">
-        <v>7.658199999999999</v>
+        <v>-2.7703</v>
       </c>
       <c r="U6" t="n">
-        <v>1.6048</v>
+        <v>-0.2291</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.8087</v>
+        <v>0.4428000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>18.3343</v>
+        <v>12.3614</v>
       </c>
       <c r="X6" t="n">
-        <v>-21.143</v>
+        <v>-11.9186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Y. MAKOUNDOU</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="D7" t="n">
-        <v>9.279400000000001</v>
+        <v>11.1329</v>
       </c>
       <c r="E7" t="n">
-        <v>5.5928</v>
+        <v>8.9899</v>
       </c>
       <c r="F7" t="n">
-        <v>3.686599999999999</v>
+        <v>2.143200000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2303</v>
+        <v>2.567500000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1103</v>
+        <v>6.8409</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8798000000000001</v>
+        <v>-4.2736</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9596</v>
+        <v>21.9865</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3043</v>
+        <v>12.6887</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3447</v>
+        <v>9.297800000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7291000000000001</v>
+        <v>-19.419</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.194</v>
+        <v>-5.8476</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5351000000000001</v>
+        <v>-13.5715</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6237</v>
+        <v>16.9325</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>-34.0974</v>
       </c>
       <c r="R7" t="n">
-        <v>3.9432</v>
+        <v>51.0298</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2061</v>
+        <v>7.242</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5501</v>
+        <v>7.037</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7561</v>
+        <v>0.2048999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>5.2192</v>
+        <v>-15.609</v>
       </c>
       <c r="W7" t="n">
-        <v>5.5028</v>
+        <v>14.063</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2836</v>
+        <v>-29.672</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. NEDOVIC</t>
+          <t>D. THEIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="n">
-        <v>7.3947</v>
+        <v>9.6866</v>
       </c>
       <c r="E8" t="n">
-        <v>3.113</v>
+        <v>25.5043</v>
       </c>
       <c r="F8" t="n">
-        <v>4.2815</v>
+        <v>-15.8179</v>
       </c>
       <c r="G8" t="n">
-        <v>12.9999</v>
+        <v>-5.939999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5888</v>
+        <v>17.8647</v>
       </c>
       <c r="I8" t="n">
-        <v>8.410600000000001</v>
+        <v>-23.8048</v>
       </c>
       <c r="J8" t="n">
-        <v>26.255</v>
+        <v>35.2675</v>
       </c>
       <c r="K8" t="n">
-        <v>10.2915</v>
+        <v>39.8404</v>
       </c>
       <c r="L8" t="n">
-        <v>15.9639</v>
+        <v>-4.572800000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-13.2553</v>
+        <v>-41.2078</v>
       </c>
       <c r="N8" t="n">
-        <v>-5.7022</v>
+        <v>-21.9758</v>
       </c>
       <c r="O8" t="n">
-        <v>-7.5529</v>
+        <v>-19.2322</v>
       </c>
       <c r="P8" t="n">
-        <v>9.0463</v>
+        <v>9.278499999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-25.2833</v>
+        <v>-39.8964</v>
       </c>
       <c r="R8" t="n">
-        <v>34.3292</v>
+        <v>49.1744</v>
       </c>
       <c r="S8" t="n">
-        <v>-15.0945</v>
+        <v>7.3103</v>
       </c>
       <c r="T8" t="n">
-        <v>-10.221</v>
+        <v>2.6672</v>
       </c>
       <c r="U8" t="n">
-        <v>-4.8736</v>
+        <v>4.6432</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4428000000000001</v>
+        <v>-0.9614999999999998</v>
       </c>
       <c r="W8" t="n">
-        <v>12.3614</v>
+        <v>27.4655</v>
       </c>
       <c r="X8" t="n">
-        <v>-11.9186</v>
+        <v>-28.427</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. STRAZEL</t>
+          <t>Y. MAKOUNDOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>3.935300000000001</v>
+        <v>9.404399999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>5.3997</v>
+        <v>6.0646</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.464400000000001</v>
+        <v>3.3396</v>
       </c>
       <c r="G9" t="n">
-        <v>26.5309</v>
+        <v>2.2303</v>
       </c>
       <c r="H9" t="n">
-        <v>6.365100000000001</v>
+        <v>3.1103</v>
       </c>
       <c r="I9" t="n">
-        <v>20.1658</v>
+        <v>-0.8798000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>65.9825</v>
+        <v>2.9596</v>
       </c>
       <c r="K9" t="n">
-        <v>24.3975</v>
+        <v>3.3043</v>
       </c>
       <c r="L9" t="n">
-        <v>41.5853</v>
+        <v>-0.3447</v>
       </c>
       <c r="M9" t="n">
-        <v>-39.4516</v>
+        <v>-0.7291000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-18.0323</v>
+        <v>-0.194</v>
       </c>
       <c r="O9" t="n">
-        <v>-21.4197</v>
+        <v>-0.5351000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-10.2059</v>
+        <v>1.6237</v>
       </c>
       <c r="Q9" t="n">
-        <v>-77.4722</v>
+        <v>-2.3195</v>
       </c>
       <c r="R9" t="n">
-        <v>67.2663</v>
+        <v>3.9432</v>
       </c>
       <c r="S9" t="n">
-        <v>-38.1533</v>
+        <v>0.3310999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-24.4039</v>
+        <v>-0.07829999999999997</v>
       </c>
       <c r="U9" t="n">
-        <v>-13.7493</v>
+        <v>0.4093</v>
       </c>
       <c r="V9" t="n">
-        <v>25.7639</v>
+        <v>5.2192</v>
       </c>
       <c r="W9" t="n">
-        <v>41.2934</v>
+        <v>5.5028</v>
       </c>
       <c r="X9" t="n">
-        <v>-15.5294</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>E. OKOBO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7452999999999992</v>
+        <v>8.793400000000002</v>
       </c>
       <c r="E10" t="n">
-        <v>11.0483</v>
+        <v>8.5388</v>
       </c>
       <c r="F10" t="n">
-        <v>-10.303</v>
+        <v>0.2545999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-27.7469</v>
+        <v>8.626099999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3932</v>
+        <v>3.112199999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-33.1406</v>
+        <v>5.513200000000002</v>
       </c>
       <c r="J10" t="n">
-        <v>25.2535</v>
+        <v>51.5711</v>
       </c>
       <c r="K10" t="n">
-        <v>28.0089</v>
+        <v>18.7965</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.754700000000001</v>
+        <v>32.7746</v>
       </c>
       <c r="M10" t="n">
-        <v>-53.0011</v>
+        <v>-42.9451</v>
       </c>
       <c r="N10" t="n">
-        <v>-22.6151</v>
+        <v>-15.6838</v>
       </c>
       <c r="O10" t="n">
-        <v>-30.3858</v>
+        <v>-27.2615</v>
       </c>
       <c r="P10" t="n">
-        <v>27.1386</v>
+        <v>1.1598</v>
       </c>
       <c r="Q10" t="n">
-        <v>-52.6536</v>
+        <v>-67.4984</v>
       </c>
       <c r="R10" t="n">
-        <v>79.7919</v>
+        <v>68.65819999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>3.861699999999999</v>
+        <v>-12.126</v>
       </c>
       <c r="T10" t="n">
-        <v>6.662199999999999</v>
+        <v>-9.0076</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.8002</v>
+        <v>-3.118400000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.5076</v>
+        <v>11.1337</v>
       </c>
       <c r="W10" t="n">
-        <v>31.7854</v>
+        <v>33.4733</v>
       </c>
       <c r="X10" t="n">
-        <v>-34.293</v>
+        <v>-22.3396</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. BEGARIN</t>
+          <t>J. BLOSSOMGAME</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5481000000000011</v>
+        <v>7.585100000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>4.767</v>
+        <v>10.7399</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.218900000000001</v>
+        <v>-3.1547</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.486000000000001</v>
+        <v>-22.4868</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3139</v>
+        <v>11.2027</v>
       </c>
       <c r="I11" t="n">
-        <v>-8.7997</v>
+        <v>-33.689</v>
       </c>
       <c r="J11" t="n">
-        <v>3.706</v>
+        <v>26.4171</v>
       </c>
       <c r="K11" t="n">
-        <v>4.7241</v>
+        <v>33.0154</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.0183</v>
+        <v>-6.598400000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-8.191600000000001</v>
+        <v>-48.9038</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4101</v>
+        <v>-21.8131</v>
       </c>
       <c r="O11" t="n">
-        <v>-7.7814</v>
+        <v>-27.091</v>
       </c>
       <c r="P11" t="n">
-        <v>6.4947</v>
+        <v>30.8499</v>
       </c>
       <c r="Q11" t="n">
-        <v>-8.582599999999999</v>
+        <v>-34.3294</v>
       </c>
       <c r="R11" t="n">
-        <v>15.0771</v>
+        <v>65.1789</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1711</v>
+        <v>2.0313</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3212</v>
+        <v>0.3172999999999998</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.1499</v>
+        <v>1.7138</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.632</v>
+        <v>-2.8087</v>
       </c>
       <c r="W11" t="n">
-        <v>6.3225</v>
+        <v>18.3343</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.954499999999999</v>
+        <v>-21.143</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. JAMES</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9195999999999995</v>
+        <v>0.5169999999999992</v>
       </c>
       <c r="E12" t="n">
-        <v>3.955999999999999</v>
+        <v>6.408300000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.876099999999999</v>
+        <v>-5.8912</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.4212</v>
+        <v>-27.7469</v>
       </c>
       <c r="H12" t="n">
-        <v>-7.079800000000001</v>
+        <v>5.3932</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6579999999999995</v>
+        <v>-33.1406</v>
       </c>
       <c r="J12" t="n">
-        <v>47.6589</v>
+        <v>25.2535</v>
       </c>
       <c r="K12" t="n">
-        <v>17.2074</v>
+        <v>28.0089</v>
       </c>
       <c r="L12" t="n">
-        <v>30.452</v>
+        <v>-2.754700000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-54.0806</v>
+        <v>-53.0011</v>
       </c>
       <c r="N12" t="n">
-        <v>-24.2865</v>
+        <v>-22.6151</v>
       </c>
       <c r="O12" t="n">
-        <v>-29.7937</v>
+        <v>-30.3858</v>
       </c>
       <c r="P12" t="n">
-        <v>-17.6285</v>
+        <v>27.1386</v>
       </c>
       <c r="Q12" t="n">
-        <v>-94.8686</v>
+        <v>-52.6536</v>
       </c>
       <c r="R12" t="n">
-        <v>77.23999999999999</v>
+        <v>79.7919</v>
       </c>
       <c r="S12" t="n">
-        <v>-31.7874</v>
+        <v>3.6336</v>
       </c>
       <c r="T12" t="n">
-        <v>-27.7172</v>
+        <v>2.0222</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.0696</v>
+        <v>1.6114</v>
       </c>
       <c r="V12" t="n">
-        <v>54.9172</v>
+        <v>-2.5076</v>
       </c>
       <c r="W12" t="n">
-        <v>78.8824</v>
+        <v>31.7854</v>
       </c>
       <c r="X12" t="n">
-        <v>-23.9653</v>
+        <v>-34.293</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. MICHINEAU</t>
+          <t>J. BEGARIN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.736</v>
+        <v>-0.7005999999999992</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4945</v>
+        <v>1.9245</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7585000000000001</v>
+        <v>-2.6247</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7226999999999999</v>
+        <v>-4.486000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7695</v>
+        <v>4.3139</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0469</v>
+        <v>-8.7997</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.8763000000000001</v>
+        <v>3.706</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7156000000000001</v>
+        <v>4.7241</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1606</v>
+        <v>-1.0183</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1536</v>
+        <v>-8.191600000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0539</v>
+        <v>-0.4101</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2076</v>
+        <v>-7.7814</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.3917</v>
+        <v>6.4947</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.3195</v>
+        <v>-8.582599999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9278</v>
+        <v>15.0771</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6215999999999999</v>
+        <v>-0.07729999999999992</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2988</v>
+        <v>0.4781999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3229</v>
+        <v>-0.5555</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-2.632</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>6.3225</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-8.954499999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. OKOBO</t>
+          <t>D. MICHINEAU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-18.7277</v>
+        <v>-2.3829</v>
       </c>
       <c r="E14" t="n">
-        <v>-12.6218</v>
+        <v>-3.3766</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.106399999999999</v>
+        <v>0.9937</v>
       </c>
       <c r="G14" t="n">
-        <v>8.626099999999999</v>
+        <v>-0.7226999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>3.112199999999999</v>
+        <v>-0.7695</v>
       </c>
       <c r="I14" t="n">
-        <v>5.513200000000002</v>
+        <v>0.0469</v>
       </c>
       <c r="J14" t="n">
-        <v>51.5711</v>
+        <v>-0.8763000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>18.7965</v>
+        <v>-0.7156000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>32.7746</v>
+        <v>-0.1606</v>
       </c>
       <c r="M14" t="n">
-        <v>-42.9451</v>
+        <v>0.1536</v>
       </c>
       <c r="N14" t="n">
-        <v>-15.6838</v>
+        <v>-0.0539</v>
       </c>
       <c r="O14" t="n">
-        <v>-27.2615</v>
+        <v>0.2076</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q14" t="n">
-        <v>-67.4984</v>
+        <v>-2.3195</v>
       </c>
       <c r="R14" t="n">
-        <v>68.65819999999999</v>
+        <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>-39.6468</v>
+        <v>-0.2684</v>
       </c>
       <c r="T14" t="n">
-        <v>-30.1679</v>
+        <v>-0.1808</v>
       </c>
       <c r="U14" t="n">
-        <v>-9.4793</v>
+        <v>-0.0877</v>
       </c>
       <c r="V14" t="n">
-        <v>11.1337</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>33.4733</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-22.3396</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,19 +1579,19 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>145.4337</v>
+        <v>183.0373</v>
       </c>
       <c r="E15" t="n">
-        <v>156.024</v>
+        <v>166.1065</v>
       </c>
       <c r="F15" t="n">
-        <v>-10.5909</v>
+        <v>16.931</v>
       </c>
       <c r="G15" t="n">
-        <v>-7.901999999999999</v>
+        <v>-7.902000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>59.76520000000001</v>
+        <v>59.7652</v>
       </c>
       <c r="I15" t="n">
         <v>-67.6687</v>
@@ -1618,19 +1618,19 @@
         <v>107.8594</v>
       </c>
       <c r="Q15" t="n">
-        <v>-470.8668000000001</v>
+        <v>-470.8668</v>
       </c>
       <c r="R15" t="n">
-        <v>578.7240999999999</v>
+        <v>578.7241</v>
       </c>
       <c r="S15" t="n">
-        <v>-43.95609999999999</v>
+        <v>-6.3525</v>
       </c>
       <c r="T15" t="n">
-        <v>-24.1022</v>
+        <v>-14.0207</v>
       </c>
       <c r="U15" t="n">
-        <v>-19.85400000000001</v>
+        <v>7.668699999999998</v>
       </c>
       <c r="V15" t="n">
         <v>89.4353</v>
